--- a/project/Lab_02_rubric.xlsx
+++ b/project/Lab_02_rubric.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ohsuitg-my.sharepoint.com/personal/wakim_ohsu_edu/Documents/Teaching/Classes/PUBH_523_26Su/PUBH_523_26Su_site/project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wakim/Library/CloudStorage/OneDrive-OregonHealth&amp;ScienceUniversity/Teaching/Classes/PUBH_523_26Su/PUBH_523_26Su_site/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{CB0C3AA1-382F-CC49-8374-443CDB6BB17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B2B0CF2-4415-004E-A16D-CD099F90D3C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CB1906-7C0D-0C40-9DF2-CD83E19404B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23920" yWindow="620" windowWidth="23000" windowHeight="22520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,10 +188,17 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,6 +223,18 @@
         <bgColor rgb="FFFCD5B5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFCD5B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -330,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -338,24 +357,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,6 +480,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -651,14 +709,13 @@
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="15">
         <v>0.5</v>
       </c>
-      <c r="D2" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D2" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -675,14 +732,13 @@
       <c r="A3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="15">
         <v>0.5</v>
       </c>
-      <c r="D3" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D3" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -701,14 +757,13 @@
       <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D4" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -727,14 +782,13 @@
       <c r="A5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="17">
         <v>1.5</v>
       </c>
-      <c r="D5" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D5" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -753,14 +807,13 @@
       <c r="A6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="17">
         <v>0.5</v>
       </c>
-      <c r="D6" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D6" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -779,14 +832,13 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="17">
         <v>1</v>
       </c>
-      <c r="D7" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D7" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -811,8 +863,7 @@
       <c r="C8" s="4">
         <v>1.5</v>
       </c>
-      <c r="D8" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D8" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -837,8 +888,7 @@
       <c r="C9" s="4">
         <v>0.5</v>
       </c>
-      <c r="D9" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D9" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -863,8 +913,7 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D10" s="16" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -886,11 +935,10 @@
       <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="17">
         <v>1</v>
       </c>
-      <c r="D11" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D11" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -912,11 +960,10 @@
       <c r="B12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="17">
         <v>1.5</v>
       </c>
-      <c r="D12" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D12" s="18" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -941,8 +988,7 @@
       <c r="C13" s="4">
         <v>1.5</v>
       </c>
-      <c r="D13" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D13" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -956,8 +1002,7 @@
       <c r="C14" s="4">
         <v>0.5</v>
       </c>
-      <c r="D14" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D14" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -971,8 +1016,7 @@
       <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D15" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -986,8 +1030,7 @@
       <c r="C16" s="11">
         <v>1.5</v>
       </c>
-      <c r="D16" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D16" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1001,8 +1044,7 @@
       <c r="C17" s="11">
         <v>1</v>
       </c>
-      <c r="D17" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D17" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1016,8 +1058,7 @@
       <c r="C18" s="11">
         <v>1</v>
       </c>
-      <c r="D18" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D18" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1031,8 +1072,7 @@
       <c r="C19" s="4">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D19" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1046,8 +1086,7 @@
       <c r="C20" s="4">
         <v>1.5</v>
       </c>
-      <c r="D20" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D20" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1061,8 +1100,7 @@
       <c r="C21" s="4">
         <v>0.5</v>
       </c>
-      <c r="D21" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D21" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1076,8 +1114,7 @@
       <c r="C22" s="4">
         <v>1.5</v>
       </c>
-      <c r="D22" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D22" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1091,8 +1128,7 @@
       <c r="C23" s="11">
         <v>1</v>
       </c>
-      <c r="D23" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D23" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1106,8 +1142,7 @@
       <c r="C24" s="11">
         <v>1.5</v>
       </c>
-      <c r="D24" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D24" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1121,8 +1156,7 @@
       <c r="C25" s="11">
         <v>1</v>
       </c>
-      <c r="D25" s="11" t="b">
-        <f>FALSE()</f>
+      <c r="D25" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1136,8 +1170,7 @@
       <c r="C26" s="4">
         <v>0.5</v>
       </c>
-      <c r="D26" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D26" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1151,8 +1184,7 @@
       <c r="C27" s="4">
         <v>0.5</v>
       </c>
-      <c r="D27" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D27" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1166,8 +1198,7 @@
       <c r="C28" s="4">
         <v>0.5</v>
       </c>
-      <c r="D28" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D28" s="16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1181,8 +1212,7 @@
       <c r="C29" s="4">
         <v>0.5</v>
       </c>
-      <c r="D29" s="4" t="b">
-        <f>FALSE()</f>
+      <c r="D29" s="16" t="b">
         <v>0</v>
       </c>
     </row>
